--- a/artfynd/A 33367-2025 artfynd.xlsx
+++ b/artfynd/A 33367-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121639357</v>
+        <v>121639361</v>
       </c>
       <c r="B2" t="n">
-        <v>56577</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590689</v>
+        <v>590612</v>
       </c>
       <c r="R2" t="n">
-        <v>6761140</v>
+        <v>6761529</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En tupp brakar iväg.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121639361</v>
+        <v>121639351</v>
       </c>
       <c r="B3" t="n">
-        <v>79250</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590612</v>
+        <v>590654</v>
       </c>
       <c r="R3" t="n">
-        <v>6761529</v>
+        <v>6761189</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,6 +849,11 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre hackspår.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,6 +875,430 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121639357</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>590689</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6761140</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En tupp brakar iväg.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121639363</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>590623</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6761438</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska gnagspår.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121639356</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>590666</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6761135</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hörd lockande.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>JMN0138 NVI Ockelbo-Grönviken</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121639353</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ockelbo-Grönviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>590673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6761166</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska gnagspår.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>JMN0138 NVI Ockelbo-Grönviken</t>
         </is>
